--- a/July_31/Cleaned.xlsx
+++ b/July_31/Cleaned.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
   <si>
     <t>CustomerID</t>
   </si>
@@ -71,6 +71,36 @@
   </si>
   <si>
     <t>Liam O'Brien</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>2021-03-23</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>2021-03-27</t>
   </si>
   <si>
     <t>India</t>
@@ -158,9 +188,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -190,9 +217,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,20 +552,20 @@
       <c r="C2">
         <v>34</v>
       </c>
-      <c r="D2" s="1">
-        <v>44270</v>
+      <c r="D2" t="s">
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -552,20 +578,20 @@
       <c r="C3">
         <v>29</v>
       </c>
-      <c r="D3" s="1">
-        <v>44271</v>
+      <c r="D3" t="s">
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -575,20 +601,20 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1">
-        <v>44272</v>
+      <c r="D4" t="s">
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -598,20 +624,20 @@
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1">
-        <v>44272</v>
+      <c r="D5" t="s">
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -624,20 +650,20 @@
       <c r="C6">
         <v>27</v>
       </c>
-      <c r="D6" s="1">
-        <v>44275</v>
+      <c r="D6" t="s">
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -650,20 +676,20 @@
       <c r="C7">
         <v>52</v>
       </c>
-      <c r="D7" s="1">
-        <v>44276</v>
+      <c r="D7" t="s">
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -676,20 +702,20 @@
       <c r="C8">
         <v>33</v>
       </c>
-      <c r="D8" s="1">
-        <v>44277</v>
+      <c r="D8" t="s">
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -699,20 +725,20 @@
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1">
-        <v>44278</v>
+      <c r="D9" t="s">
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -722,20 +748,20 @@
       <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="1">
-        <v>44280</v>
+      <c r="D10" t="s">
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -745,20 +771,20 @@
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="1">
-        <v>44281</v>
+      <c r="D11" t="s">
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -771,20 +797,20 @@
       <c r="C12">
         <v>31</v>
       </c>
-      <c r="D12" s="1">
-        <v>44282</v>
+      <c r="D12" t="s">
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/July_31/Cleaned.xlsx
+++ b/July_31/Cleaned.xlsx
@@ -73,34 +73,34 @@
     <t>Liam O'Brien</t>
   </si>
   <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>2021-03-23</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-03-27</t>
+    <t>15-03-2021</t>
+  </si>
+  <si>
+    <t>16-03-2021</t>
+  </si>
+  <si>
+    <t>17-03-2021</t>
+  </si>
+  <si>
+    <t>20-03-2021</t>
+  </si>
+  <si>
+    <t>21-03-2021</t>
+  </si>
+  <si>
+    <t>22-03-2021</t>
+  </si>
+  <si>
+    <t>23-03-2021</t>
+  </si>
+  <si>
+    <t>25-03-2021</t>
+  </si>
+  <si>
+    <t>26-03-2021</t>
+  </si>
+  <si>
+    <t>27-03-2021</t>
   </si>
   <si>
     <t>India</t>
